--- a/pav_3g_results_element.xlsx
+++ b/pav_3g_results_element.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -488,7 +488,7 @@
         <v>13.3293328219011</v>
       </c>
       <c r="C2" t="n">
-        <v>337.2695627275129</v>
+        <v>333.8848254407104</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>175.0122316608172</v>
+        <v>173.2558608180466</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3.488206098933006e-11</v>
       </c>
       <c r="H2" t="n">
         <v>11.13329964228579</v>
@@ -512,7 +512,7 @@
         <v>30.50875810084839</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4525505391311233</v>
+        <v>2.222664250705292</v>
       </c>
     </row>
     <row r="3">
@@ -523,7 +523,7 @@
         <v>11.92620796388136</v>
       </c>
       <c r="C3" t="n">
-        <v>625.8612525614425</v>
+        <v>620.1794475652387</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -532,10 +532,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>397.1059129017733</v>
+        <v>393.5008353376844</v>
       </c>
       <c r="G3" t="n">
-        <v>245.6123408853767</v>
+        <v>243.1474482886527</v>
       </c>
       <c r="H3" t="n">
         <v>15.03542838536893</v>
@@ -547,7 +547,7 @@
         <v>41.1933243942569</v>
       </c>
       <c r="K3" t="n">
-        <v>1.927478523809255</v>
+        <v>0.5215236563569332</v>
       </c>
     </row>
     <row r="4">
@@ -558,7 +558,7 @@
         <v>10.5230984612139</v>
       </c>
       <c r="C4" t="n">
-        <v>822.913490816106</v>
+        <v>815.7292712588185</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>648.3402844040139</v>
+        <v>642.68012813852</v>
       </c>
       <c r="G4" t="n">
-        <v>802.553320676006</v>
+        <v>795.0324043649958</v>
       </c>
       <c r="H4" t="n">
         <v>20.85700578759742</v>
@@ -582,7 +582,7 @@
         <v>57.13138917018539</v>
       </c>
       <c r="K4" t="n">
-        <v>4.621116600123874</v>
+        <v>0.2186124348771666</v>
       </c>
     </row>
     <row r="5">
@@ -593,7 +593,7 @@
         <v>9.11998902430812</v>
       </c>
       <c r="C5" t="n">
-        <v>897.9960599331073</v>
+        <v>890.0266441418962</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -602,10 +602,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>897.7637848030341</v>
+        <v>889.7964303762579</v>
       </c>
       <c r="G5" t="n">
-        <v>1714.343376201173</v>
+        <v>1698.862471478712</v>
       </c>
       <c r="H5" t="n">
         <v>29.81908969989933</v>
@@ -617,7 +617,7 @@
         <v>81.66401868197437</v>
       </c>
       <c r="K5" t="n">
-        <v>8.59472901856522</v>
+        <v>0.1180948824134216</v>
       </c>
     </row>
     <row r="6">
@@ -628,7 +628,7 @@
         <v>7.716897869149379</v>
       </c>
       <c r="C6" t="n">
-        <v>926.9347789616651</v>
+        <v>918.4780674099809</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1156.953952185862</v>
+        <v>1146.398704854277</v>
       </c>
       <c r="G6" t="n">
-        <v>2978.324550274719</v>
+        <v>2951.626233830709</v>
       </c>
       <c r="H6" t="n">
         <v>41.56038618177409</v>
@@ -652,7 +652,7 @@
         <v>113.8005263867832</v>
       </c>
       <c r="K6" t="n">
-        <v>13.86351921868897</v>
+        <v>0.07339016187602024</v>
       </c>
     </row>
     <row r="7">
@@ -663,7 +663,7 @@
         <v>6.31380669755022</v>
       </c>
       <c r="C7" t="n">
-        <v>935.5258614047722</v>
+        <v>926.7149648432276</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -672,10 +672,10 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1425.831136760593</v>
+        <v>1412.402485369561</v>
       </c>
       <c r="G7" t="n">
-        <v>4607.225239502581</v>
+        <v>4565.665960251368</v>
       </c>
       <c r="H7" t="n">
         <v>56.03850053290055</v>
@@ -687,7 +687,7 @@
         <v>153.4238521439835</v>
       </c>
       <c r="K7" t="n">
-        <v>20.47764253258408</v>
+        <v>0.05000452653821974</v>
       </c>
     </row>
     <row r="8">
@@ -698,7 +698,7 @@
         <v>4.91071552595106</v>
       </c>
       <c r="C8" t="n">
-        <v>930.9463650052941</v>
+        <v>921.870108851575</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1701.377148470709</v>
+        <v>1684.789581888804</v>
       </c>
       <c r="G8" t="n">
-        <v>6614.683984931149</v>
+        <v>6554.218214595862</v>
       </c>
       <c r="H8" t="n">
         <v>73.54015248127043</v>
@@ -722,7 +722,7 @@
         <v>201.3179603616919</v>
       </c>
       <c r="K8" t="n">
-        <v>28.47686941287734</v>
+        <v>0.0365754992398053</v>
       </c>
     </row>
     <row r="9">
@@ -733,7 +733,7 @@
         <v>3.541482800910612</v>
       </c>
       <c r="C9" t="n">
-        <v>872.8310726117072</v>
+        <v>864.0656596851638</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -742,10 +742,10 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1987.147194107166</v>
+        <v>1967.191252747267</v>
       </c>
       <c r="G9" t="n">
-        <v>9007.839350408081</v>
+        <v>8924.040476463557</v>
       </c>
       <c r="H9" t="n">
         <v>95.0524409160797</v>
@@ -757,7 +757,7 @@
         <v>260.4777634332362</v>
       </c>
       <c r="K9" t="n">
-        <v>37.82771421455472</v>
+        <v>0.02924147113208047</v>
       </c>
     </row>
     <row r="10">
@@ -768,7 +768,7 @@
         <v>2.138443199620908</v>
       </c>
       <c r="C10" t="n">
-        <v>903.6782435344323</v>
+        <v>894.3196798145029</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2297.73744415073</v>
+        <v>2273.941892540856</v>
       </c>
       <c r="G10" t="n">
-        <v>11649.68579295419</v>
+        <v>11539.33903847612</v>
       </c>
       <c r="H10" t="n">
         <v>131.1626716055017</v>
@@ -792,7 +792,7 @@
         <v>359.352111215017</v>
       </c>
       <c r="K10" t="n">
-        <v>49.15137882138144</v>
+        <v>0.02254106063296369</v>
       </c>
     </row>
     <row r="11">
@@ -803,7 +803,7 @@
         <v>0.7015453687862842</v>
       </c>
       <c r="C11" t="n">
-        <v>853.1687190745215</v>
+        <v>844.0198199279531</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -812,10 +812,10 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2614.389296532946</v>
+        <v>2586.354063326313</v>
       </c>
       <c r="G11" t="n">
-        <v>14983.81667906162</v>
+        <v>14838.91432209117</v>
       </c>
       <c r="H11" t="n">
         <v>158.1238467263724</v>
@@ -827,7 +827,7 @@
         <v>432.6988362282643</v>
       </c>
       <c r="K11" t="n">
-        <v>62.65878110441299</v>
+        <v>0.01955387002372674</v>
       </c>
     </row>
     <row r="12">
@@ -838,7 +838,7 @@
         <v>-0.7015452734313519</v>
       </c>
       <c r="C12" t="n">
-        <v>853.4171916819231</v>
+        <v>844.2668949221351</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>-2614.439928077669</v>
+        <v>-2586.408032967394</v>
       </c>
       <c r="G12" t="n">
-        <v>18646.69199200984</v>
+        <v>18462.56229190006</v>
       </c>
       <c r="H12" t="n">
         <v>158.0415340872649</v>
@@ -862,7 +862,7 @@
         <v>432.5107126974885</v>
       </c>
       <c r="K12" t="n">
-        <v>62.6862491483604</v>
+        <v>0.01954531311979214</v>
       </c>
     </row>
     <row r="13">
@@ -873,7 +873,7 @@
         <v>-2.138400551527386</v>
       </c>
       <c r="C13" t="n">
-        <v>904.2670374912317</v>
+        <v>894.9044061261911</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -882,10 +882,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>-2297.963454271704</v>
+        <v>-2274.170720686767</v>
       </c>
       <c r="G13" t="n">
-        <v>15077.63455762272</v>
+        <v>14931.83275025341</v>
       </c>
       <c r="H13" t="n">
         <v>131.0098595088716</v>
@@ -897,7 +897,7 @@
         <v>359.002049802268</v>
       </c>
       <c r="K13" t="n">
-        <v>49.19173898403093</v>
+        <v>0.02252340077982427</v>
       </c>
     </row>
     <row r="14">
@@ -908,7 +908,7 @@
         <v>-3.541419204433926</v>
       </c>
       <c r="C14" t="n">
-        <v>873.5564153246366</v>
+        <v>864.78631200007</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -917,10 +917,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>-1987.510904179759</v>
+        <v>-1967.557211799173</v>
       </c>
       <c r="G14" t="n">
-        <v>11678.79904100141</v>
+        <v>11568.21371131751</v>
       </c>
       <c r="H14" t="n">
         <v>94.9405338476687</v>
@@ -932,7 +932,7 @@
         <v>260.221311185631</v>
       </c>
       <c r="K14" t="n">
-        <v>37.85960683100402</v>
+        <v>0.02921627929591227</v>
       </c>
     </row>
     <row r="15">
@@ -943,7 +943,7 @@
         <v>-4.91067343847586</v>
       </c>
       <c r="C15" t="n">
-        <v>931.6159064490794</v>
+        <v>922.535754732826</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -952,10 +952,10 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>-1701.676930506061</v>
+        <v>-1685.091249010077</v>
       </c>
       <c r="G15" t="n">
-        <v>9012.017504123331</v>
+        <v>8928.207139639404</v>
       </c>
       <c r="H15" t="n">
         <v>73.46382858579754</v>
@@ -967,7 +967,7 @@
         <v>201.143415819404</v>
       </c>
       <c r="K15" t="n">
-        <v>28.49896325506473</v>
+        <v>0.03654709716719925</v>
       </c>
     </row>
     <row r="16">
@@ -978,7 +978,7 @@
         <v>-6.31376461007502</v>
       </c>
       <c r="C16" t="n">
-        <v>936.2359146907116</v>
+        <v>927.4212292303437</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -987,10 +987,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>-1426.13868462043</v>
+        <v>-1412.711551853484</v>
       </c>
       <c r="G16" t="n">
-        <v>6616.189777221789</v>
+        <v>6555.73075216396</v>
       </c>
       <c r="H16" t="n">
         <v>55.98033776640718</v>
@@ -1002,7 +1002,7 @@
         <v>153.2908183332579</v>
       </c>
       <c r="K16" t="n">
-        <v>20.49374250638927</v>
+        <v>0.04996512382177237</v>
       </c>
     </row>
     <row r="17">
@@ -1013,7 +1013,7 @@
         <v>-7.716855781674179</v>
       </c>
       <c r="C17" t="n">
-        <v>927.6396865499323</v>
+        <v>919.1793289963221</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1022,10 +1022,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-1157.204843849744</v>
+        <v>-1146.650781875296</v>
       </c>
       <c r="G17" t="n">
-        <v>4608.298301604603</v>
+        <v>4566.743626955204</v>
       </c>
       <c r="H17" t="n">
         <v>41.51724765868896</v>
@@ -1037,7 +1037,7 @@
         <v>113.7018374824549</v>
       </c>
       <c r="K17" t="n">
-        <v>13.87451579896513</v>
+        <v>0.07333177804996512</v>
       </c>
     </row>
     <row r="18">
@@ -1048,7 +1048,7 @@
         <v>-9.119946936832919</v>
       </c>
       <c r="C18" t="n">
-        <v>898.6924593661862</v>
+        <v>890.7195950637866</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1057,10 +1057,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-897.9716041540607</v>
+        <v>-890.0051350103156</v>
       </c>
       <c r="G18" t="n">
-        <v>2979.044593351512</v>
+        <v>2952.349210641647</v>
       </c>
       <c r="H18" t="n">
         <v>29.78813594098335</v>
@@ -1072,7 +1072,7 @@
         <v>81.59318781441304</v>
       </c>
       <c r="K18" t="n">
-        <v>8.601622086280626</v>
+        <v>0.1179998861222019</v>
       </c>
     </row>
     <row r="19">
@@ -1083,7 +1083,7 @@
         <v>-10.5230637719277</v>
       </c>
       <c r="C19" t="n">
-        <v>823.5477617976479</v>
+        <v>816.3603466779736</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-648.4794598768457</v>
+        <v>-642.8199325357012</v>
       </c>
       <c r="G19" t="n">
-        <v>1715.027634685142</v>
+        <v>1699.546032623309</v>
       </c>
       <c r="H19" t="n">
         <v>20.83530823042767</v>
@@ -1107,7 +1107,7 @@
         <v>57.08172400600177</v>
       </c>
       <c r="K19" t="n">
-        <v>4.62489398819895</v>
+        <v>0.218433091493768</v>
       </c>
     </row>
     <row r="20">
@@ -1118,7 +1118,7 @@
         <v>-11.92618068922458</v>
       </c>
       <c r="C20" t="n">
-        <v>626.3769706186472</v>
+        <v>620.6926878803787</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1127,10 +1127,10 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-397.2156585554874</v>
+        <v>-393.6109824302728</v>
       </c>
       <c r="G20" t="n">
-        <v>803.1070853604543</v>
+        <v>795.5839493507981</v>
       </c>
       <c r="H20" t="n">
         <v>15.01974570569714</v>
@@ -1142,7 +1142,7 @@
         <v>41.15741590687573</v>
       </c>
       <c r="K20" t="n">
-        <v>1.929094280709044</v>
+        <v>0.5210849647793908</v>
       </c>
     </row>
     <row r="21">
@@ -1153,7 +1153,7 @@
         <v>-13.32927197590668</v>
       </c>
       <c r="C21" t="n">
-        <v>337.5478961336943</v>
+        <v>334.1617514797422</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -1162,10 +1162,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-175.0694776767505</v>
+        <v>-173.3132511302663</v>
       </c>
       <c r="G21" t="n">
-        <v>245.6809126371058</v>
+        <v>243.2163405914614</v>
       </c>
       <c r="H21" t="n">
         <v>11.12174078320303</v>
@@ -1177,7 +1177,7 @@
         <v>30.48226737205935</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4529288330465115</v>
+        <v>2.220793395056997</v>
       </c>
     </row>
   </sheetData>

--- a/pav_3g_results_element.xlsx
+++ b/pav_3g_results_element.xlsx
@@ -488,7 +488,7 @@
         <v>13.3293328219011</v>
       </c>
       <c r="C2" t="n">
-        <v>333.8848254407104</v>
+        <v>421.9202329875313</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -497,22 +497,22 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>173.2558608180466</v>
+        <v>173.2558608180106</v>
       </c>
       <c r="G2" t="n">
-        <v>3.488206098933006e-11</v>
+        <v>1.341617730358848e-11</v>
       </c>
       <c r="H2" t="n">
-        <v>11.13329964228579</v>
+        <v>8.810290469653527</v>
       </c>
       <c r="I2" t="n">
-        <v>64.43423902592149</v>
+        <v>50.87335933042844</v>
       </c>
       <c r="J2" t="n">
-        <v>30.50875810084839</v>
+        <v>24.13181740421857</v>
       </c>
       <c r="K2" t="n">
-        <v>2.222664250705292</v>
+        <v>0.9169955926580481</v>
       </c>
     </row>
     <row r="3">
@@ -523,7 +523,7 @@
         <v>11.92620796388136</v>
       </c>
       <c r="C3" t="n">
-        <v>620.1794475652387</v>
+        <v>513.0160402288334</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -532,22 +532,22 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>393.5008353376844</v>
+        <v>393.5008353376811</v>
       </c>
       <c r="G3" t="n">
-        <v>243.1474482886527</v>
+        <v>243.1474482885722</v>
       </c>
       <c r="H3" t="n">
-        <v>15.03542838536893</v>
+        <v>18.17616397683456</v>
       </c>
       <c r="I3" t="n">
-        <v>86.92896047546363</v>
+        <v>89.46545303890777</v>
       </c>
       <c r="J3" t="n">
-        <v>41.1933243942569</v>
+        <v>45.16640189795145</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5215236563569332</v>
+        <v>1.000000000000131</v>
       </c>
     </row>
     <row r="4">
@@ -558,7 +558,7 @@
         <v>10.5230984612139</v>
       </c>
       <c r="C4" t="n">
-        <v>815.7292712588185</v>
+        <v>512.7136455535443</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -567,22 +567,22 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>642.68012813852</v>
+        <v>642.6801281386312</v>
       </c>
       <c r="G4" t="n">
-        <v>795.0324043649958</v>
+        <v>795.0324043649449</v>
       </c>
       <c r="H4" t="n">
-        <v>20.85700578759742</v>
+        <v>33.1835719203238</v>
       </c>
       <c r="I4" t="n">
-        <v>120.4662756484653</v>
+        <v>150.6889806168377</v>
       </c>
       <c r="J4" t="n">
-        <v>57.13138917018539</v>
+        <v>75.11158536012418</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2186124348771666</v>
+        <v>0.9999999999999944</v>
       </c>
     </row>
     <row r="5">
@@ -593,7 +593,7 @@
         <v>9.11998902430812</v>
       </c>
       <c r="C5" t="n">
-        <v>890.0266441418962</v>
+        <v>459.7071715165018</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -602,22 +602,22 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>889.7964303762579</v>
+        <v>889.7964303763364</v>
       </c>
       <c r="G5" t="n">
-        <v>1698.862471478712</v>
+        <v>1698.862471478519</v>
       </c>
       <c r="H5" t="n">
-        <v>29.81908969989933</v>
+        <v>57.73193454742108</v>
       </c>
       <c r="I5" t="n">
-        <v>172.0614002386529</v>
+        <v>249.832635218672</v>
       </c>
       <c r="J5" t="n">
-        <v>81.66401868197437</v>
+        <v>120.5175882956265</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1180948824134216</v>
+        <v>0.9999999999999726</v>
       </c>
     </row>
     <row r="6">
@@ -628,7 +628,7 @@
         <v>7.716897869149379</v>
       </c>
       <c r="C6" t="n">
-        <v>918.4780674099809</v>
+        <v>407.2806441749121</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -637,22 +637,22 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1146.398704854277</v>
+        <v>1146.398704854317</v>
       </c>
       <c r="G6" t="n">
-        <v>2951.626233830709</v>
+        <v>2951.626233830736</v>
       </c>
       <c r="H6" t="n">
-        <v>41.56038618177409</v>
+        <v>93.72481537485936</v>
       </c>
       <c r="I6" t="n">
-        <v>239.6173484840924</v>
+        <v>392.5666503917664</v>
       </c>
       <c r="J6" t="n">
-        <v>113.8005263867832</v>
+        <v>182.2719789450041</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07339016187602024</v>
+        <v>0.9999999999999359</v>
       </c>
     </row>
     <row r="7">
@@ -663,7 +663,7 @@
         <v>6.31380669755022</v>
       </c>
       <c r="C7" t="n">
-        <v>926.7149648432276</v>
+        <v>363.1287884612193</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -672,22 +672,22 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1412.402485369561</v>
+        <v>1412.402485369548</v>
       </c>
       <c r="G7" t="n">
-        <v>4565.665960251368</v>
+        <v>4565.665960251052</v>
       </c>
       <c r="H7" t="n">
-        <v>56.03850053290055</v>
+        <v>143.0118423584043</v>
       </c>
       <c r="I7" t="n">
-        <v>322.8799446276303</v>
+        <v>584.982561151192</v>
       </c>
       <c r="J7" t="n">
-        <v>153.4238521439835</v>
+        <v>261.3028246212751</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05000452653821974</v>
+        <v>0.9999999999999322</v>
       </c>
     </row>
     <row r="8">
@@ -698,7 +698,7 @@
         <v>4.91071552595106</v>
       </c>
       <c r="C8" t="n">
-        <v>921.870108851575</v>
+        <v>326.4480213670884</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -707,22 +707,22 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1684.789581888804</v>
+        <v>1684.789581888817</v>
       </c>
       <c r="G8" t="n">
-        <v>6554.218214595862</v>
+        <v>6554.218214595685</v>
       </c>
       <c r="H8" t="n">
-        <v>73.54015248127043</v>
+        <v>207.6730870935023</v>
       </c>
       <c r="I8" t="n">
-        <v>423.4908811134301</v>
+        <v>834.4994063585997</v>
       </c>
       <c r="J8" t="n">
-        <v>201.3179603616919</v>
+        <v>359.4072702244815</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0365754992398053</v>
+        <v>0.9999999999999233</v>
       </c>
     </row>
     <row r="9">
@@ -733,7 +733,7 @@
         <v>3.541482800910612</v>
       </c>
       <c r="C9" t="n">
-        <v>864.0656596851638</v>
+        <v>284.287317228867</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -742,22 +742,22 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1967.191252747267</v>
+        <v>1967.191252747214</v>
       </c>
       <c r="G9" t="n">
-        <v>8924.040476463557</v>
+        <v>8924.040476463346</v>
       </c>
       <c r="H9" t="n">
-        <v>95.0524409160797</v>
+        <v>288.9033209973344</v>
       </c>
       <c r="I9" t="n">
-        <v>550.0608988273269</v>
+        <v>1153.670892545158</v>
       </c>
       <c r="J9" t="n">
-        <v>260.4777634332362</v>
+        <v>480.8807261092844</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02924147113208047</v>
+        <v>0.9999999999999177</v>
       </c>
     </row>
     <row r="10">
@@ -768,7 +768,7 @@
         <v>2.138443199620908</v>
       </c>
       <c r="C10" t="n">
-        <v>894.3196798145029</v>
+        <v>268.9986250958891</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -777,22 +777,22 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2273.941892540856</v>
+        <v>2273.941892540915</v>
       </c>
       <c r="G10" t="n">
-        <v>11539.33903847612</v>
+        <v>11539.33903847604</v>
       </c>
       <c r="H10" t="n">
-        <v>131.1626716055017</v>
+        <v>436.0667584528916</v>
       </c>
       <c r="I10" t="n">
-        <v>758.2112035154032</v>
+        <v>1715.626795714514</v>
       </c>
       <c r="J10" t="n">
-        <v>359.352111215017</v>
+        <v>688.9227730536517</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02254106063296369</v>
+        <v>0.9999999999999151</v>
       </c>
     </row>
     <row r="11">
@@ -803,7 +803,7 @@
         <v>0.7015453687862842</v>
       </c>
       <c r="C11" t="n">
-        <v>844.0198199279531</v>
+        <v>239.5072293440943</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -812,22 +812,22 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2586.354063326313</v>
+        <v>2586.354063326326</v>
       </c>
       <c r="G11" t="n">
-        <v>14838.91432209117</v>
+        <v>14838.91432209111</v>
       </c>
       <c r="H11" t="n">
-        <v>158.1238467263724</v>
+        <v>557.2260219693413</v>
       </c>
       <c r="I11" t="n">
-        <v>908.8703436915612</v>
+        <v>2160.030327660271</v>
       </c>
       <c r="J11" t="n">
-        <v>432.6988362282643</v>
+        <v>848.2098868816441</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01955387002372674</v>
+        <v>0.9999999999999061</v>
       </c>
     </row>
     <row r="12">
@@ -838,7 +838,7 @@
         <v>-0.7015452734313519</v>
       </c>
       <c r="C12" t="n">
-        <v>844.2668949221351</v>
+        <v>239.5415629990008</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -847,22 +847,22 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>-2586.408032967394</v>
+        <v>-2586.408032967146</v>
       </c>
       <c r="G12" t="n">
-        <v>18462.56229190006</v>
+        <v>18462.5622918984</v>
       </c>
       <c r="H12" t="n">
-        <v>158.0415340872649</v>
+        <v>557.0191393179282</v>
       </c>
       <c r="I12" t="n">
-        <v>908.7664474737904</v>
+        <v>2160.222615503509</v>
       </c>
       <c r="J12" t="n">
-        <v>432.5107126974885</v>
+        <v>847.9613149312947</v>
       </c>
       <c r="K12" t="n">
-        <v>0.01954531311979214</v>
+        <v>0.9999999999999777</v>
       </c>
     </row>
     <row r="13">
@@ -873,7 +873,7 @@
         <v>-2.138400551527386</v>
       </c>
       <c r="C13" t="n">
-        <v>894.9044061261911</v>
+        <v>269.1003485140653</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -882,22 +882,22 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>-2274.170720686767</v>
+        <v>-2274.170720686596</v>
       </c>
       <c r="G13" t="n">
-        <v>14931.83275025341</v>
+        <v>14931.83275025206</v>
       </c>
       <c r="H13" t="n">
-        <v>131.0098595088716</v>
+        <v>435.6787390571667</v>
       </c>
       <c r="I13" t="n">
-        <v>758.0157190010459</v>
+        <v>1715.864945505881</v>
       </c>
       <c r="J13" t="n">
-        <v>359.002049802268</v>
+        <v>688.4514598861846</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02252340077982427</v>
+        <v>0.9999999999999758</v>
       </c>
     </row>
     <row r="14">
@@ -908,7 +908,7 @@
         <v>-3.541419204433926</v>
       </c>
       <c r="C14" t="n">
-        <v>864.78631200007</v>
+        <v>284.4404018597155</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -917,22 +917,22 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>-1967.557211799173</v>
+        <v>-1967.557211798964</v>
       </c>
       <c r="G14" t="n">
-        <v>11568.21371131751</v>
+        <v>11568.21371131632</v>
       </c>
       <c r="H14" t="n">
-        <v>94.9405338476687</v>
+        <v>288.6484254298252</v>
       </c>
       <c r="I14" t="n">
-        <v>549.9175154313515</v>
+        <v>1153.837982643411</v>
       </c>
       <c r="J14" t="n">
-        <v>260.221311185631</v>
+        <v>480.5486391208058</v>
       </c>
       <c r="K14" t="n">
-        <v>0.02921627929591227</v>
+        <v>0.9999999999999676</v>
       </c>
     </row>
     <row r="15">
@@ -943,7 +943,7 @@
         <v>-4.91067343847586</v>
       </c>
       <c r="C15" t="n">
-        <v>922.535754732826</v>
+        <v>326.5971811218021</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -952,22 +952,22 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>-1685.091249010077</v>
+        <v>-1685.091249009842</v>
       </c>
       <c r="G15" t="n">
-        <v>8928.207139639404</v>
+        <v>8928.207139638362</v>
       </c>
       <c r="H15" t="n">
-        <v>73.46382858579754</v>
+        <v>207.5125336880485</v>
       </c>
       <c r="I15" t="n">
-        <v>423.3944281172987</v>
+        <v>834.6046818854629</v>
       </c>
       <c r="J15" t="n">
-        <v>201.143415819404</v>
+        <v>359.1881398205825</v>
       </c>
       <c r="K15" t="n">
-        <v>0.03654709716719925</v>
+        <v>0.9999999999999499</v>
       </c>
     </row>
     <row r="16">
@@ -978,7 +978,7 @@
         <v>-6.31376461007502</v>
       </c>
       <c r="C16" t="n">
-        <v>927.4212292303437</v>
+        <v>363.3082359101717</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -987,22 +987,22 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>-1412.711551853484</v>
+        <v>-1412.711551853354</v>
       </c>
       <c r="G16" t="n">
-        <v>6555.73075216396</v>
+        <v>6555.730752162865</v>
       </c>
       <c r="H16" t="n">
-        <v>55.98033776640718</v>
+        <v>142.9016700763226</v>
       </c>
       <c r="I16" t="n">
-        <v>322.8064157105599</v>
+        <v>585.0506995677163</v>
       </c>
       <c r="J16" t="n">
-        <v>153.2908183332579</v>
+        <v>261.1424095555968</v>
       </c>
       <c r="K16" t="n">
-        <v>0.04996512382177237</v>
+        <v>0.9999999999999276</v>
       </c>
     </row>
     <row r="17">
@@ -1013,7 +1013,7 @@
         <v>-7.716855781674179</v>
       </c>
       <c r="C17" t="n">
-        <v>919.1793289963221</v>
+        <v>407.4819437893545</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1022,22 +1022,22 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-1146.650781875296</v>
+        <v>-1146.650781874904</v>
       </c>
       <c r="G17" t="n">
-        <v>4566.743626955204</v>
+        <v>4566.743626954114</v>
       </c>
       <c r="H17" t="n">
-        <v>41.51724765868896</v>
+        <v>93.65272848606293</v>
       </c>
       <c r="I17" t="n">
-        <v>239.5627891164772</v>
+        <v>392.6065272155275</v>
       </c>
       <c r="J17" t="n">
-        <v>113.7018374824549</v>
+        <v>182.1590397309019</v>
       </c>
       <c r="K17" t="n">
-        <v>0.07333177804996512</v>
+        <v>0.9999999999998767</v>
       </c>
     </row>
     <row r="18">
@@ -1048,7 +1048,7 @@
         <v>-9.119946936832919</v>
       </c>
       <c r="C18" t="n">
-        <v>890.7195950637866</v>
+        <v>459.9407207602134</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1057,22 +1057,22 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-890.0051350103156</v>
+        <v>-890.0051350098053</v>
       </c>
       <c r="G18" t="n">
-        <v>2952.349210641647</v>
+        <v>2952.349210641002</v>
       </c>
       <c r="H18" t="n">
-        <v>29.78813594098335</v>
+        <v>57.68760013071233</v>
       </c>
       <c r="I18" t="n">
-        <v>172.0222302919203</v>
+        <v>249.8529033823248</v>
       </c>
       <c r="J18" t="n">
-        <v>81.59318781441304</v>
+        <v>120.4421248200506</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1179998861222019</v>
+        <v>0.9999999999998694</v>
       </c>
     </row>
     <row r="19">
@@ -1083,7 +1083,7 @@
         <v>-10.5230637719277</v>
       </c>
       <c r="C19" t="n">
-        <v>816.3603466779736</v>
+        <v>512.970308027539</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1092,22 +1092,22 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-642.8199325357012</v>
+        <v>-642.8199325355049</v>
       </c>
       <c r="G19" t="n">
-        <v>1699.546032623309</v>
+        <v>1699.546032623191</v>
       </c>
       <c r="H19" t="n">
-        <v>20.83530823042767</v>
+        <v>33.15809742582412</v>
       </c>
       <c r="I19" t="n">
-        <v>120.4387969869539</v>
+        <v>150.6968645888823</v>
       </c>
       <c r="J19" t="n">
-        <v>57.08172400600177</v>
+        <v>75.06394584317243</v>
       </c>
       <c r="K19" t="n">
-        <v>0.218433091493768</v>
+        <v>0.9999999999998979</v>
       </c>
     </row>
     <row r="20">
@@ -1118,7 +1118,7 @@
         <v>-11.92618068922458</v>
       </c>
       <c r="C20" t="n">
-        <v>620.6926878803787</v>
+        <v>513.299807031073</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1127,22 +1127,22 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-393.6109824302728</v>
+        <v>-393.610982430384</v>
       </c>
       <c r="G20" t="n">
-        <v>795.5839493507981</v>
+        <v>795.5839493508786</v>
       </c>
       <c r="H20" t="n">
-        <v>15.01974570569714</v>
+        <v>18.16218554078871</v>
       </c>
       <c r="I20" t="n">
-        <v>86.90908254584787</v>
+        <v>89.46596997191899</v>
       </c>
       <c r="J20" t="n">
-        <v>41.15741590687573</v>
+        <v>45.13736654285712</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5210849647793908</v>
+        <v>0.9999999999999956</v>
       </c>
     </row>
     <row r="21">
@@ -1153,7 +1153,7 @@
         <v>-13.32927197590668</v>
       </c>
       <c r="C21" t="n">
-        <v>334.1617514797422</v>
+        <v>422.1316176503665</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -1162,22 +1162,22 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-173.3132511302663</v>
+        <v>-173.3132511303138</v>
       </c>
       <c r="G21" t="n">
-        <v>243.2163405914614</v>
+        <v>243.2163405915003</v>
       </c>
       <c r="H21" t="n">
-        <v>11.12174078320303</v>
+        <v>8.804032259668242</v>
       </c>
       <c r="I21" t="n">
-        <v>64.41941375128134</v>
+        <v>50.87114233095912</v>
       </c>
       <c r="J21" t="n">
-        <v>30.48226737205935</v>
+        <v>24.11750396648271</v>
       </c>
       <c r="K21" t="n">
-        <v>2.220793395056997</v>
+        <v>0.9167930259386406</v>
       </c>
     </row>
   </sheetData>

--- a/pav_3g_results_element.xlsx
+++ b/pav_3g_results_element.xlsx
@@ -488,7 +488,7 @@
         <v>13.3293328219011</v>
       </c>
       <c r="C2" t="n">
-        <v>421.9202329875313</v>
+        <v>460.6701778772726</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -497,22 +497,22 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>173.2558608180106</v>
+        <v>173.2558608180188</v>
       </c>
       <c r="G2" t="n">
-        <v>1.341617730358848e-11</v>
+        <v>-3.354044325897121e-12</v>
       </c>
       <c r="H2" t="n">
-        <v>8.810290469653527</v>
+        <v>8.069200018052776</v>
       </c>
       <c r="I2" t="n">
-        <v>50.87335933042844</v>
+        <v>28.66055339076268</v>
       </c>
       <c r="J2" t="n">
-        <v>24.13181740421857</v>
+        <v>7.619227077725417</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9169955926580481</v>
+        <v>0.9999999999999424</v>
       </c>
     </row>
     <row r="3">
@@ -523,7 +523,7 @@
         <v>11.92620796388136</v>
       </c>
       <c r="C3" t="n">
-        <v>513.0160402288334</v>
+        <v>532.6051116218262</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -532,22 +532,22 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>393.5008353376811</v>
+        <v>393.5008353376288</v>
       </c>
       <c r="G3" t="n">
-        <v>243.1474482885722</v>
+        <v>243.1474482885132</v>
       </c>
       <c r="H3" t="n">
-        <v>18.17616397683456</v>
+        <v>17.50764960094167</v>
       </c>
       <c r="I3" t="n">
-        <v>89.46545303890777</v>
+        <v>60.77267980891965</v>
       </c>
       <c r="J3" t="n">
-        <v>45.16640189795145</v>
+        <v>11.26015580966121</v>
       </c>
       <c r="K3" t="n">
-        <v>1.000000000000131</v>
+        <v>1.000000000000008</v>
       </c>
     </row>
     <row r="4">
@@ -558,7 +558,7 @@
         <v>10.5230984612139</v>
       </c>
       <c r="C4" t="n">
-        <v>512.7136455535443</v>
+        <v>523.7485192120683</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -567,22 +567,22 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>642.6801281386312</v>
+        <v>642.6801281385266</v>
       </c>
       <c r="G4" t="n">
-        <v>795.0324043649449</v>
+        <v>795.0324043648725</v>
       </c>
       <c r="H4" t="n">
-        <v>33.1835719203238</v>
+        <v>32.48442622301058</v>
       </c>
       <c r="I4" t="n">
-        <v>150.6889806168377</v>
+        <v>112.304171022744</v>
       </c>
       <c r="J4" t="n">
-        <v>75.11158536012418</v>
+        <v>17.72295745884351</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9999999999999944</v>
+        <v>1.000000000025082</v>
       </c>
     </row>
     <row r="5">
@@ -593,7 +593,7 @@
         <v>9.11998902430812</v>
       </c>
       <c r="C5" t="n">
-        <v>459.7071715165018</v>
+        <v>467.8557861241389</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -605,19 +605,19 @@
         <v>889.7964303763364</v>
       </c>
       <c r="G5" t="n">
-        <v>1698.862471478519</v>
+        <v>1698.862471478278</v>
       </c>
       <c r="H5" t="n">
-        <v>57.73193454742108</v>
+        <v>56.72642109832957</v>
       </c>
       <c r="I5" t="n">
-        <v>249.832635218672</v>
+        <v>197.2596114460551</v>
       </c>
       <c r="J5" t="n">
-        <v>120.5175882956265</v>
+        <v>33.24098971637958</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9999999999999726</v>
+        <v>1.00000000001833</v>
       </c>
     </row>
     <row r="6">
@@ -628,7 +628,7 @@
         <v>7.716897869149379</v>
       </c>
       <c r="C6" t="n">
-        <v>407.2806441749121</v>
+        <v>413.9767482320098</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -637,22 +637,22 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1146.398704854317</v>
+        <v>1146.398704854382</v>
       </c>
       <c r="G6" t="n">
-        <v>2951.626233830736</v>
+        <v>2951.626233830435</v>
       </c>
       <c r="H6" t="n">
-        <v>93.72481537485936</v>
+        <v>92.20880965917955</v>
       </c>
       <c r="I6" t="n">
-        <v>392.5666503917664</v>
+        <v>319.8203409121043</v>
       </c>
       <c r="J6" t="n">
-        <v>182.2719789450041</v>
+        <v>49.77012256706394</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9999999999999359</v>
+        <v>1.000000000007128</v>
       </c>
     </row>
     <row r="7">
@@ -663,7 +663,7 @@
         <v>6.31380669755022</v>
       </c>
       <c r="C7" t="n">
-        <v>363.1287884612193</v>
+        <v>368.4467714349432</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -672,22 +672,22 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1412.402485369548</v>
+        <v>1412.402485369796</v>
       </c>
       <c r="G7" t="n">
-        <v>4565.665960251052</v>
+        <v>4565.665960250885</v>
       </c>
       <c r="H7" t="n">
-        <v>143.0118423584043</v>
+        <v>140.9476784094718</v>
       </c>
       <c r="I7" t="n">
-        <v>584.982561151192</v>
+        <v>490.3688825786277</v>
       </c>
       <c r="J7" t="n">
-        <v>261.3028246212751</v>
+        <v>79.71260831289031</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9999999999999322</v>
+        <v>1.000000000003381</v>
       </c>
     </row>
     <row r="8">
@@ -698,7 +698,7 @@
         <v>4.91071552595106</v>
       </c>
       <c r="C8" t="n">
-        <v>326.4480213670884</v>
+        <v>330.8064914764738</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -707,22 +707,22 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1684.789581888817</v>
+        <v>1684.789581888555</v>
       </c>
       <c r="G8" t="n">
-        <v>6554.218214595685</v>
+        <v>6554.218214595734</v>
       </c>
       <c r="H8" t="n">
-        <v>207.6730870935023</v>
+        <v>204.9369347931349</v>
       </c>
       <c r="I8" t="n">
-        <v>834.4994063585997</v>
+        <v>710.582239099728</v>
       </c>
       <c r="J8" t="n">
-        <v>359.4072702244815</v>
+        <v>106.622871933004</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9999999999999233</v>
+        <v>1.000000000001778</v>
       </c>
     </row>
     <row r="9">
@@ -733,7 +733,7 @@
         <v>3.541482800910612</v>
       </c>
       <c r="C9" t="n">
-        <v>284.287317228867</v>
+        <v>286.1355687770171</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -742,22 +742,22 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1967.191252747214</v>
+        <v>1967.191252746926</v>
       </c>
       <c r="G9" t="n">
-        <v>8924.040476463346</v>
+        <v>8924.040476463244</v>
       </c>
       <c r="H9" t="n">
-        <v>288.9033209973344</v>
+        <v>287.0371915517906</v>
       </c>
       <c r="I9" t="n">
-        <v>1153.670892545158</v>
+        <v>1005.572705873896</v>
       </c>
       <c r="J9" t="n">
-        <v>480.8807261092844</v>
+        <v>163.0396318638597</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9999999999999177</v>
+        <v>1.000000000028394</v>
       </c>
     </row>
     <row r="10">
@@ -768,7 +768,7 @@
         <v>2.138443199620908</v>
       </c>
       <c r="C10" t="n">
-        <v>268.9986250958891</v>
+        <v>267.8494951076101</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -777,22 +777,22 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2273.941892540915</v>
+        <v>2273.941892540719</v>
       </c>
       <c r="G10" t="n">
-        <v>11539.33903847604</v>
+        <v>11539.33903847553</v>
       </c>
       <c r="H10" t="n">
-        <v>436.0667584528916</v>
+        <v>437.9375754533881</v>
       </c>
       <c r="I10" t="n">
-        <v>1715.626795714514</v>
+        <v>1594.601460593421</v>
       </c>
       <c r="J10" t="n">
-        <v>688.9227730536517</v>
+        <v>430.1704218657391</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9999999999999151</v>
+        <v>1.000000000091414</v>
       </c>
     </row>
     <row r="11">
@@ -803,7 +803,7 @@
         <v>0.7015453687862842</v>
       </c>
       <c r="C11" t="n">
-        <v>239.5072293440943</v>
+        <v>238.1948967557465</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -812,22 +812,22 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2586.354063326326</v>
+        <v>2586.354063326182</v>
       </c>
       <c r="G11" t="n">
-        <v>14838.91432209111</v>
+        <v>14838.91432209043</v>
       </c>
       <c r="H11" t="n">
-        <v>557.2260219693413</v>
+        <v>560.2960536016624</v>
       </c>
       <c r="I11" t="n">
-        <v>2160.030327660271</v>
+        <v>2104.785669795175</v>
       </c>
       <c r="J11" t="n">
-        <v>848.2098868816441</v>
+        <v>727.7861982674402</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9999999999999061</v>
+        <v>1.000000000041687</v>
       </c>
     </row>
     <row r="12">
@@ -838,7 +838,7 @@
         <v>-0.7015452734313519</v>
       </c>
       <c r="C12" t="n">
-        <v>239.5415629990008</v>
+        <v>238.2306699282938</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -847,22 +847,22 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>-2586.408032967146</v>
+        <v>-2586.408032967212</v>
       </c>
       <c r="G12" t="n">
-        <v>18462.5622918984</v>
+        <v>18462.5622918991</v>
       </c>
       <c r="H12" t="n">
-        <v>557.0191393179282</v>
+        <v>560.0842044928053</v>
       </c>
       <c r="I12" t="n">
-        <v>2160.222615503509</v>
+        <v>2105.041115698151</v>
       </c>
       <c r="J12" t="n">
-        <v>847.9613149312947</v>
+        <v>727.6935069378853</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9999999999999777</v>
+        <v>1.00000000018345</v>
       </c>
     </row>
     <row r="13">
@@ -873,7 +873,7 @@
         <v>-2.138400551527386</v>
       </c>
       <c r="C13" t="n">
-        <v>269.1003485140653</v>
+        <v>267.9494550884232</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -882,22 +882,22 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>-2274.170720686596</v>
+        <v>-2274.170720686727</v>
       </c>
       <c r="G13" t="n">
-        <v>14931.83275025206</v>
+        <v>14931.83275025274</v>
       </c>
       <c r="H13" t="n">
-        <v>435.6787390571667</v>
+        <v>437.5500613791781</v>
       </c>
       <c r="I13" t="n">
-        <v>1715.864945505881</v>
+        <v>1594.980157667842</v>
       </c>
       <c r="J13" t="n">
-        <v>688.4514598861846</v>
+        <v>430.0470579566469</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9999999999999758</v>
+        <v>1.000000000123214</v>
       </c>
     </row>
     <row r="14">
@@ -908,7 +908,7 @@
         <v>-3.541419204433926</v>
       </c>
       <c r="C14" t="n">
-        <v>284.4404018597155</v>
+        <v>286.2878204440819</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -917,22 +917,22 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>-1967.557211798964</v>
+        <v>-1967.557211799121</v>
       </c>
       <c r="G14" t="n">
-        <v>11568.21371131632</v>
+        <v>11568.21371131681</v>
       </c>
       <c r="H14" t="n">
-        <v>288.6484254298252</v>
+        <v>286.785773834441</v>
       </c>
       <c r="I14" t="n">
-        <v>1153.837982643411</v>
+        <v>1005.855814064969</v>
       </c>
       <c r="J14" t="n">
-        <v>480.5486391208058</v>
+        <v>163.0408589171253</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9999999999999676</v>
+        <v>1.000000000052197</v>
       </c>
     </row>
     <row r="15">
@@ -943,7 +943,7 @@
         <v>-4.91067343847586</v>
       </c>
       <c r="C15" t="n">
-        <v>326.5971811218021</v>
+        <v>330.9533937800709</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -952,22 +952,22 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>-1685.091249009842</v>
+        <v>-1685.09124900996</v>
       </c>
       <c r="G15" t="n">
-        <v>8928.207139638362</v>
+        <v>8928.20713963878</v>
       </c>
       <c r="H15" t="n">
-        <v>207.5125336880485</v>
+        <v>204.7811257526974</v>
       </c>
       <c r="I15" t="n">
-        <v>834.6046818854629</v>
+        <v>710.7722380653023</v>
       </c>
       <c r="J15" t="n">
-        <v>359.1881398205825</v>
+        <v>106.6361370088537</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9999999999999499</v>
+        <v>1.000000000003288</v>
       </c>
     </row>
     <row r="16">
@@ -978,7 +978,7 @@
         <v>-6.31376461007502</v>
       </c>
       <c r="C16" t="n">
-        <v>363.3082359101717</v>
+        <v>368.6237065680234</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -987,22 +987,22 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>-1412.711551853354</v>
+        <v>-1412.71155185338</v>
       </c>
       <c r="G16" t="n">
-        <v>6555.730752162865</v>
+        <v>6555.730752163413</v>
       </c>
       <c r="H16" t="n">
-        <v>142.9016700763226</v>
+        <v>140.8410602438147</v>
       </c>
       <c r="I16" t="n">
-        <v>585.0506995677163</v>
+        <v>490.5000620297475</v>
       </c>
       <c r="J16" t="n">
-        <v>261.1424095555968</v>
+        <v>79.71697609301677</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9999999999999276</v>
+        <v>1.000000000006287</v>
       </c>
     </row>
     <row r="17">
@@ -1013,7 +1013,7 @@
         <v>-7.716855781674179</v>
       </c>
       <c r="C17" t="n">
-        <v>407.4819437893545</v>
+        <v>414.1750255815481</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1022,22 +1022,22 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-1146.650781874904</v>
+        <v>-1146.650781875166</v>
       </c>
       <c r="G17" t="n">
-        <v>4566.743626954114</v>
+        <v>4566.743626954784</v>
       </c>
       <c r="H17" t="n">
-        <v>93.65272848606293</v>
+        <v>92.13929736854637</v>
       </c>
       <c r="I17" t="n">
-        <v>392.6065272155275</v>
+        <v>319.9077808377339</v>
       </c>
       <c r="J17" t="n">
-        <v>182.1590397309019</v>
+        <v>49.77790676290574</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9999999999998767</v>
+        <v>1.000000000013174</v>
       </c>
     </row>
     <row r="18">
@@ -1048,7 +1048,7 @@
         <v>-9.119946936832919</v>
       </c>
       <c r="C18" t="n">
-        <v>459.9407207602134</v>
+        <v>468.0857371279067</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1057,22 +1057,22 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-890.0051350098053</v>
+        <v>-890.0051350100539</v>
       </c>
       <c r="G18" t="n">
-        <v>2952.349210641002</v>
+        <v>2952.349210641469</v>
       </c>
       <c r="H18" t="n">
-        <v>57.68760013071233</v>
+        <v>56.68379589144267</v>
       </c>
       <c r="I18" t="n">
-        <v>249.8529033823248</v>
+        <v>197.3128982586202</v>
       </c>
       <c r="J18" t="n">
-        <v>120.4421248200506</v>
+        <v>33.24315425419633</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9999999999998694</v>
+        <v>1.000000000033802</v>
       </c>
     </row>
     <row r="19">
@@ -1083,7 +1083,7 @@
         <v>-10.5230637719277</v>
       </c>
       <c r="C19" t="n">
-        <v>512.970308027539</v>
+        <v>524.0012980895962</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1092,22 +1092,22 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-642.8199325355049</v>
+        <v>-642.8199325356685</v>
       </c>
       <c r="G19" t="n">
-        <v>1699.546032623191</v>
+        <v>1699.546032623325</v>
       </c>
       <c r="H19" t="n">
-        <v>33.15809742582412</v>
+        <v>32.46007121002853</v>
       </c>
       <c r="I19" t="n">
-        <v>150.6968645888823</v>
+        <v>112.3350609720914</v>
       </c>
       <c r="J19" t="n">
-        <v>75.06394584317243</v>
+        <v>17.72565441474681</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9999999999998979</v>
+        <v>1.000000000045953</v>
       </c>
     </row>
     <row r="20">
@@ -1118,7 +1118,7 @@
         <v>-11.92618068922458</v>
       </c>
       <c r="C20" t="n">
-        <v>513.299807031073</v>
+        <v>532.8839345423854</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1127,22 +1127,22 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-393.610982430384</v>
+        <v>-393.6109824304003</v>
       </c>
       <c r="G20" t="n">
-        <v>795.5839493508786</v>
+        <v>795.5839493508598</v>
       </c>
       <c r="H20" t="n">
-        <v>18.16218554078871</v>
+        <v>17.49470330974807</v>
       </c>
       <c r="I20" t="n">
-        <v>89.46596997191899</v>
+        <v>60.78757802880959</v>
       </c>
       <c r="J20" t="n">
-        <v>45.13736654285712</v>
+        <v>11.25417389475067</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9999999999999956</v>
+        <v>0.9999999999998822</v>
       </c>
     </row>
     <row r="21">
@@ -1153,7 +1153,7 @@
         <v>-13.32927197590668</v>
       </c>
       <c r="C21" t="n">
-        <v>422.1316176503665</v>
+        <v>460.9111422377319</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -1162,22 +1162,22 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-173.3132511303138</v>
+        <v>-173.3132511303105</v>
       </c>
       <c r="G21" t="n">
-        <v>243.2163405915003</v>
+        <v>243.2163405915043</v>
       </c>
       <c r="H21" t="n">
-        <v>8.804032259668242</v>
+        <v>8.063290380823666</v>
       </c>
       <c r="I21" t="n">
-        <v>50.87114233095912</v>
+        <v>28.66676120954822</v>
       </c>
       <c r="J21" t="n">
-        <v>24.11750396648271</v>
+        <v>7.615078407476254</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9167930259386406</v>
+        <v>0.9999999999999637</v>
       </c>
     </row>
   </sheetData>
